--- a/RemasterShips/ship_data_Extract.xlsx
+++ b/RemasterShips/ship_data_Extract.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\RemasterShips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7AEF48F-C3D3-49E0-A781-D3AD38A24ABC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23FF244-0AD3-4DDE-8F4B-763E3652619E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4349" uniqueCount="1168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4971" uniqueCount="1171">
   <si>
     <t>Name</t>
   </si>
@@ -3527,6 +3527,15 @@
   </si>
   <si>
     <t>Deployable Feature</t>
+  </si>
+  <si>
+    <t>3D MODEL FILE</t>
+  </si>
+  <si>
+    <t>3D MODEL TEXTURE</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -3545,6 +3554,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -3885,7 +3895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P311"/>
+  <dimension ref="A1:R311"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -3901,9 +3911,11 @@
     <col min="13" max="13" width="50" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
     <col min="15" max="16" width="50" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3952,8 +3964,14 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1166</v>
       </c>
@@ -3987,8 +4005,14 @@
       <c r="P2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R2" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4037,8 +4061,14 @@
       <c r="P3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R3" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4087,8 +4117,14 @@
       <c r="P4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R4" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4137,8 +4173,14 @@
       <c r="P5" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R5" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -4187,8 +4229,14 @@
       <c r="P6" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R6" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -4237,8 +4285,14 @@
       <c r="P7" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R7" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -4287,8 +4341,14 @@
       <c r="P8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R8" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4337,8 +4397,14 @@
       <c r="P9" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R9" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -4387,8 +4453,14 @@
       <c r="P10" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R10" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -4437,8 +4509,14 @@
       <c r="P11" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R11" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -4487,8 +4565,14 @@
       <c r="P12" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R12" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -4537,8 +4621,14 @@
       <c r="P13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R13" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -4587,8 +4677,14 @@
       <c r="P14" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R14" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -4637,8 +4733,14 @@
       <c r="P15" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R15" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -4687,8 +4789,14 @@
       <c r="P16" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R16" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -4737,8 +4845,14 @@
       <c r="P17" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R17" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -4787,8 +4901,14 @@
       <c r="P18" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -4837,8 +4957,14 @@
       <c r="P19" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -4887,8 +5013,14 @@
       <c r="P20" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>120</v>
       </c>
@@ -4937,8 +5069,14 @@
       <c r="P21" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R21" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
@@ -4987,8 +5125,14 @@
       <c r="P22" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R22" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -5037,8 +5181,14 @@
       <c r="P23" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R23" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -5087,8 +5237,14 @@
       <c r="P24" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>135</v>
       </c>
@@ -5137,8 +5293,14 @@
       <c r="P25" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -5187,8 +5349,14 @@
       <c r="P26" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R26" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>142</v>
       </c>
@@ -5237,8 +5405,14 @@
       <c r="P27" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R27" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -5287,8 +5461,14 @@
       <c r="P28" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q28" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -5337,8 +5517,14 @@
       <c r="P29" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q29" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5387,8 +5573,14 @@
       <c r="P30" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q30" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>156</v>
       </c>
@@ -5437,8 +5629,14 @@
       <c r="P31" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q31" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>160</v>
       </c>
@@ -5487,8 +5685,14 @@
       <c r="P32" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q32" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R32" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -5537,8 +5741,14 @@
       <c r="P33" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q33" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R33" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>167</v>
       </c>
@@ -5587,8 +5797,14 @@
       <c r="P34" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q34" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R34" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>170</v>
       </c>
@@ -5637,8 +5853,14 @@
       <c r="P35" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q35" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R35" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>174</v>
       </c>
@@ -5687,8 +5909,14 @@
       <c r="P36" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q36" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>177</v>
       </c>
@@ -5737,8 +5965,14 @@
       <c r="P37" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q37" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R37" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>180</v>
       </c>
@@ -5787,8 +6021,14 @@
       <c r="P38" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q38" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R38" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -5837,8 +6077,14 @@
       <c r="P39" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q39" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R39" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -5887,8 +6133,14 @@
       <c r="P40" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q40" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R40" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>192</v>
       </c>
@@ -5937,8 +6189,14 @@
       <c r="P41" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q41" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R41" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>195</v>
       </c>
@@ -5987,8 +6245,14 @@
       <c r="P42" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q42" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R42" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -6037,8 +6301,14 @@
       <c r="P43" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q43" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R43" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>201</v>
       </c>
@@ -6087,8 +6357,14 @@
       <c r="P44" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q44" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R44" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>205</v>
       </c>
@@ -6137,8 +6413,14 @@
       <c r="P45" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q45" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R45" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>208</v>
       </c>
@@ -6187,8 +6469,14 @@
       <c r="P46" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q46" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R46" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -6237,8 +6525,14 @@
       <c r="P47" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q47" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R47" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>215</v>
       </c>
@@ -6287,8 +6581,14 @@
       <c r="P48" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q48" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>218</v>
       </c>
@@ -6337,8 +6637,14 @@
       <c r="P49" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q49" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R49" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>221</v>
       </c>
@@ -6387,8 +6693,14 @@
       <c r="P50" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q50" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>227</v>
       </c>
@@ -6437,8 +6749,14 @@
       <c r="P51" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q51" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R51" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>230</v>
       </c>
@@ -6487,8 +6805,14 @@
       <c r="P52" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q52" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R52" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>233</v>
       </c>
@@ -6537,8 +6861,14 @@
       <c r="P53" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q53" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>238</v>
       </c>
@@ -6587,8 +6917,14 @@
       <c r="P54" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q54" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R54" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>242</v>
       </c>
@@ -6634,8 +6970,14 @@
       <c r="P55" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q55" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R55" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>247</v>
       </c>
@@ -6681,8 +7023,14 @@
       <c r="P56" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q56" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R56" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>249</v>
       </c>
@@ -6728,8 +7076,14 @@
       <c r="P57" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q57" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R57" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>252</v>
       </c>
@@ -6775,8 +7129,14 @@
       <c r="P58" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q58" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R58" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>255</v>
       </c>
@@ -6822,8 +7182,14 @@
       <c r="P59" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q59" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R59" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>258</v>
       </c>
@@ -6872,8 +7238,14 @@
       <c r="P60" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q60" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R60" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>262</v>
       </c>
@@ -6922,8 +7294,14 @@
       <c r="P61" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q61" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>266</v>
       </c>
@@ -6972,8 +7350,14 @@
       <c r="P62" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q62" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R62" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>271</v>
       </c>
@@ -7022,8 +7406,14 @@
       <c r="P63" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q63" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R63" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>276</v>
       </c>
@@ -7072,8 +7462,14 @@
       <c r="P64" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q64" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R64" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>281</v>
       </c>
@@ -7122,8 +7518,14 @@
       <c r="P65" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q65" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R65" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>286</v>
       </c>
@@ -7172,8 +7574,14 @@
       <c r="P66" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q66" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>291</v>
       </c>
@@ -7222,8 +7630,14 @@
       <c r="P67" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q67" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R67" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>297</v>
       </c>
@@ -7272,8 +7686,14 @@
       <c r="P68" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q68" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R68" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1134</v>
       </c>
@@ -7322,8 +7742,14 @@
       <c r="P69" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q69" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R69" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1135</v>
       </c>
@@ -7372,8 +7798,14 @@
       <c r="P70" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q70" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R70" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1136</v>
       </c>
@@ -7422,8 +7854,14 @@
       <c r="P71" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q71" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R71" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1137</v>
       </c>
@@ -7472,8 +7910,14 @@
       <c r="P72" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q72" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R72" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>317</v>
       </c>
@@ -7522,8 +7966,14 @@
       <c r="P73" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q73" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R73" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>321</v>
       </c>
@@ -7572,8 +8022,14 @@
       <c r="P74" t="s">
         <v>324</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q74" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R74" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>325</v>
       </c>
@@ -7622,8 +8078,14 @@
       <c r="P75" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q75" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R75" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>329</v>
       </c>
@@ -7672,8 +8134,14 @@
       <c r="P76" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q76" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R76" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>332</v>
       </c>
@@ -7722,8 +8190,14 @@
       <c r="P77" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q77" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R77" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>335</v>
       </c>
@@ -7772,8 +8246,14 @@
       <c r="P78" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q78" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R78" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>340</v>
       </c>
@@ -7822,8 +8302,14 @@
       <c r="P79" t="s">
         <v>343</v>
       </c>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q79" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R79" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>344</v>
       </c>
@@ -7872,8 +8358,14 @@
       <c r="P80" t="s">
         <v>346</v>
       </c>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q80" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R80" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>347</v>
       </c>
@@ -7922,8 +8414,14 @@
       <c r="P81" t="s">
         <v>351</v>
       </c>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q81" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R81" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>352</v>
       </c>
@@ -7972,8 +8470,14 @@
       <c r="P82" t="s">
         <v>355</v>
       </c>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q82" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R82" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>356</v>
       </c>
@@ -8022,8 +8526,14 @@
       <c r="P83" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q83" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R83" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>361</v>
       </c>
@@ -8072,8 +8582,14 @@
       <c r="P84" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q84" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R84" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>366</v>
       </c>
@@ -8122,8 +8638,14 @@
       <c r="P85" t="s">
         <v>369</v>
       </c>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q85" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R85" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>370</v>
       </c>
@@ -8172,8 +8694,14 @@
       <c r="P86" t="s">
         <v>372</v>
       </c>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q86" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R86" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>373</v>
       </c>
@@ -8222,8 +8750,14 @@
       <c r="P87" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q87" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R87" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>376</v>
       </c>
@@ -8272,8 +8806,14 @@
       <c r="P88" t="s">
         <v>378</v>
       </c>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q88" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R88" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>379</v>
       </c>
@@ -8322,8 +8862,14 @@
       <c r="P89" t="s">
         <v>382</v>
       </c>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q89" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R89" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>383</v>
       </c>
@@ -8372,8 +8918,14 @@
       <c r="P90" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q90" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R90" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>386</v>
       </c>
@@ -8422,8 +8974,14 @@
       <c r="P91" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q91" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R91" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>389</v>
       </c>
@@ -8472,8 +9030,14 @@
       <c r="P92" t="s">
         <v>391</v>
       </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q92" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R92" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>392</v>
       </c>
@@ -8522,8 +9086,14 @@
       <c r="P93" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q93" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R93" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>395</v>
       </c>
@@ -8572,8 +9142,14 @@
       <c r="P94" t="s">
         <v>397</v>
       </c>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q94" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R94" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>398</v>
       </c>
@@ -8622,8 +9198,14 @@
       <c r="P95" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q95" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R95" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>401</v>
       </c>
@@ -8672,8 +9254,14 @@
       <c r="P96" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q96" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R96" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>404</v>
       </c>
@@ -8722,8 +9310,14 @@
       <c r="P97" t="s">
         <v>407</v>
       </c>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q97" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R97" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>408</v>
       </c>
@@ -8772,8 +9366,14 @@
       <c r="P98" t="s">
         <v>410</v>
       </c>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q98" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R98" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>411</v>
       </c>
@@ -8822,8 +9422,14 @@
       <c r="P99" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q99" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R99" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>414</v>
       </c>
@@ -8872,8 +9478,14 @@
       <c r="P100" t="s">
         <v>416</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q100" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R100" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>417</v>
       </c>
@@ -8922,8 +9534,14 @@
       <c r="P101" t="s">
         <v>419</v>
       </c>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q101" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R101" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>420</v>
       </c>
@@ -8972,8 +9590,14 @@
       <c r="P102" t="s">
         <v>423</v>
       </c>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q102" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R102" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>424</v>
       </c>
@@ -9022,8 +9646,14 @@
       <c r="P103" t="s">
         <v>427</v>
       </c>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q103" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R103" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>428</v>
       </c>
@@ -9072,8 +9702,14 @@
       <c r="P104" t="s">
         <v>430</v>
       </c>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q104" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R104" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>431</v>
       </c>
@@ -9122,8 +9758,14 @@
       <c r="P105" t="s">
         <v>433</v>
       </c>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q105" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R105" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>434</v>
       </c>
@@ -9172,8 +9814,14 @@
       <c r="P106" t="s">
         <v>436</v>
       </c>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q106" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R106" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>437</v>
       </c>
@@ -9222,8 +9870,14 @@
       <c r="P107" t="s">
         <v>439</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q107" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R107" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>440</v>
       </c>
@@ -9272,8 +9926,14 @@
       <c r="P108" t="s">
         <v>442</v>
       </c>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q108" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R108" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>443</v>
       </c>
@@ -9322,8 +9982,14 @@
       <c r="P109" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q109" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R109" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>446</v>
       </c>
@@ -9372,8 +10038,14 @@
       <c r="P110" t="s">
         <v>448</v>
       </c>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q110" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R110" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>449</v>
       </c>
@@ -9422,8 +10094,14 @@
       <c r="P111" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q111" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R111" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>452</v>
       </c>
@@ -9472,8 +10150,14 @@
       <c r="P112" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q112" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R112" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>455</v>
       </c>
@@ -9522,8 +10206,14 @@
       <c r="P113" t="s">
         <v>457</v>
       </c>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q113" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R113" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>458</v>
       </c>
@@ -9572,8 +10262,14 @@
       <c r="P114" t="s">
         <v>460</v>
       </c>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q114" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R114" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>461</v>
       </c>
@@ -9622,8 +10318,14 @@
       <c r="P115" t="s">
         <v>464</v>
       </c>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q115" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R115" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>465</v>
       </c>
@@ -9672,8 +10374,14 @@
       <c r="P116" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q116" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R116" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>469</v>
       </c>
@@ -9722,8 +10430,14 @@
       <c r="P117" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q117" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R117" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>472</v>
       </c>
@@ -9772,8 +10486,14 @@
       <c r="P118" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q118" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R118" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>475</v>
       </c>
@@ -9822,8 +10542,14 @@
       <c r="P119" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q119" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R119" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>478</v>
       </c>
@@ -9872,8 +10598,14 @@
       <c r="P120" t="s">
         <v>480</v>
       </c>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q120" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R120" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>481</v>
       </c>
@@ -9922,8 +10654,14 @@
       <c r="P121" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q121" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R121" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1147</v>
       </c>
@@ -9972,8 +10710,14 @@
       <c r="P122" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q122" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R122" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1148</v>
       </c>
@@ -10022,8 +10766,14 @@
       <c r="P123" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q123" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R123" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1149</v>
       </c>
@@ -10072,8 +10822,14 @@
       <c r="P124" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q124" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R124" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1150</v>
       </c>
@@ -10122,8 +10878,14 @@
       <c r="P125" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q125" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R125" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>498</v>
       </c>
@@ -10172,8 +10934,14 @@
       <c r="P126" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q126" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R126" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>501</v>
       </c>
@@ -10222,8 +10990,14 @@
       <c r="P127" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q127" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R127" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>341</v>
       </c>
@@ -10272,8 +11046,14 @@
       <c r="P128" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q128" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R128" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>97</v>
       </c>
@@ -10322,8 +11102,14 @@
       <c r="P129" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q129" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R129" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>512</v>
       </c>
@@ -10372,8 +11158,14 @@
       <c r="P130" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q130" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R130" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>516</v>
       </c>
@@ -10422,8 +11214,14 @@
       <c r="P131" t="s">
         <v>520</v>
       </c>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q131" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R131" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>521</v>
       </c>
@@ -10472,8 +11270,14 @@
       <c r="P132" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q132" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R132" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>526</v>
       </c>
@@ -10522,8 +11326,14 @@
       <c r="P133" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q133" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R133" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>530</v>
       </c>
@@ -10572,8 +11382,14 @@
       <c r="P134" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q134" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R134" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>535</v>
       </c>
@@ -10622,8 +11438,14 @@
       <c r="P135" t="s">
         <v>537</v>
       </c>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q135" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R135" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>538</v>
       </c>
@@ -10672,8 +11494,14 @@
       <c r="P136" t="s">
         <v>542</v>
       </c>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q136" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R136" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>543</v>
       </c>
@@ -10722,8 +11550,14 @@
       <c r="P137" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q137" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R137" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>150</v>
       </c>
@@ -10772,8 +11606,14 @@
       <c r="P138" t="s">
         <v>550</v>
       </c>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q138" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R138" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>161</v>
       </c>
@@ -10822,8 +11662,14 @@
       <c r="P139" t="s">
         <v>553</v>
       </c>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q139" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R139" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>189</v>
       </c>
@@ -10872,8 +11718,14 @@
       <c r="P140" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q140" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R140" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>557</v>
       </c>
@@ -10922,8 +11774,14 @@
       <c r="P141" t="s">
         <v>560</v>
       </c>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q141" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R141" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>561</v>
       </c>
@@ -10972,8 +11830,14 @@
       <c r="P142" t="s">
         <v>563</v>
       </c>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q142" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R142" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>564</v>
       </c>
@@ -11022,8 +11886,14 @@
       <c r="P143" t="s">
         <v>566</v>
       </c>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q143" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R143" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>567</v>
       </c>
@@ -11072,8 +11942,14 @@
       <c r="P144" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q144" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R144" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>572</v>
       </c>
@@ -11122,8 +11998,14 @@
       <c r="P145" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q145" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R145" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>575</v>
       </c>
@@ -11172,8 +12054,14 @@
       <c r="P146" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q146" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R146" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>578</v>
       </c>
@@ -11222,8 +12110,14 @@
       <c r="P147" t="s">
         <v>581</v>
       </c>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q147" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R147" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>582</v>
       </c>
@@ -11272,8 +12166,14 @@
       <c r="P148" t="s">
         <v>585</v>
       </c>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q148" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R148" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>586</v>
       </c>
@@ -11322,8 +12222,14 @@
       <c r="P149" t="s">
         <v>588</v>
       </c>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q149" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R149" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>589</v>
       </c>
@@ -11372,8 +12278,14 @@
       <c r="P150" t="s">
         <v>591</v>
       </c>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q150" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R150" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>592</v>
       </c>
@@ -11422,8 +12334,14 @@
       <c r="P151" t="s">
         <v>595</v>
       </c>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q151" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R151" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>596</v>
       </c>
@@ -11472,8 +12390,14 @@
       <c r="P152" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q152" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R152" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>599</v>
       </c>
@@ -11522,8 +12446,14 @@
       <c r="P153" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q153" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R153" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>603</v>
       </c>
@@ -11572,8 +12502,14 @@
       <c r="P154" t="s">
         <v>605</v>
       </c>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q154" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R154" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>606</v>
       </c>
@@ -11622,8 +12558,14 @@
       <c r="P155" t="s">
         <v>608</v>
       </c>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q155" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R155" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>609</v>
       </c>
@@ -11672,8 +12614,14 @@
       <c r="P156" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q156" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R156" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>612</v>
       </c>
@@ -11722,8 +12670,14 @@
       <c r="P157" t="s">
         <v>614</v>
       </c>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q157" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R157" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>615</v>
       </c>
@@ -11772,8 +12726,14 @@
       <c r="P158" t="s">
         <v>618</v>
       </c>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q158" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R158" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>619</v>
       </c>
@@ -11822,8 +12782,14 @@
       <c r="P159" t="s">
         <v>623</v>
       </c>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q159" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R159" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>624</v>
       </c>
@@ -11872,8 +12838,14 @@
       <c r="P160" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q160" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R160" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1151</v>
       </c>
@@ -11922,8 +12894,14 @@
       <c r="P161" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q161" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R161" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1152</v>
       </c>
@@ -11972,8 +12950,14 @@
       <c r="P162" t="s">
         <v>634</v>
       </c>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q162" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R162" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1153</v>
       </c>
@@ -12022,8 +13006,14 @@
       <c r="P163" t="s">
         <v>638</v>
       </c>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q163" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R163" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1154</v>
       </c>
@@ -12072,8 +13062,14 @@
       <c r="P164" t="s">
         <v>641</v>
       </c>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q164" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R164" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>642</v>
       </c>
@@ -12122,8 +13118,14 @@
       <c r="P165" t="s">
         <v>645</v>
       </c>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q165" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R165" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>646</v>
       </c>
@@ -12172,8 +13174,14 @@
       <c r="P166" t="s">
         <v>650</v>
       </c>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q166" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R166" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>651</v>
       </c>
@@ -12222,8 +13230,14 @@
       <c r="P167" t="s">
         <v>655</v>
       </c>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q167" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R167" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>656</v>
       </c>
@@ -12272,8 +13286,14 @@
       <c r="P168" t="s">
         <v>658</v>
       </c>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q168" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R168" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>659</v>
       </c>
@@ -12322,8 +13342,14 @@
       <c r="P169" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q169" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R169" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>662</v>
       </c>
@@ -12372,8 +13398,14 @@
       <c r="P170" t="s">
         <v>664</v>
       </c>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q170" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R170" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>665</v>
       </c>
@@ -12422,8 +13454,14 @@
       <c r="P171" t="s">
         <v>667</v>
       </c>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q171" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R171" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>668</v>
       </c>
@@ -12472,8 +13510,14 @@
       <c r="P172" t="s">
         <v>670</v>
       </c>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q172" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R172" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>671</v>
       </c>
@@ -12522,8 +13566,14 @@
       <c r="P173" t="s">
         <v>674</v>
       </c>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q173" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R173" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>675</v>
       </c>
@@ -12572,8 +13622,14 @@
       <c r="P174" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q174" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R174" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>679</v>
       </c>
@@ -12622,8 +13678,14 @@
       <c r="P175" t="s">
         <v>681</v>
       </c>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q175" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R175" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>682</v>
       </c>
@@ -12672,8 +13734,14 @@
       <c r="P176" t="s">
         <v>684</v>
       </c>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q176" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R176" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>685</v>
       </c>
@@ -12722,8 +13790,14 @@
       <c r="P177" t="s">
         <v>689</v>
       </c>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q177" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R177" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>690</v>
       </c>
@@ -12772,8 +13846,14 @@
       <c r="P178" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q178" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R178" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>693</v>
       </c>
@@ -12822,8 +13902,14 @@
       <c r="P179" t="s">
         <v>695</v>
       </c>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q179" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R179" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>696</v>
       </c>
@@ -12872,8 +13958,14 @@
       <c r="P180" t="s">
         <v>698</v>
       </c>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q180" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R180" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>699</v>
       </c>
@@ -12922,8 +14014,14 @@
       <c r="P181" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q181" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R181" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>702</v>
       </c>
@@ -12972,8 +14070,14 @@
       <c r="P182" t="s">
         <v>704</v>
       </c>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q182" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R182" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>705</v>
       </c>
@@ -13022,8 +14126,14 @@
       <c r="P183" t="s">
         <v>707</v>
       </c>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q183" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R183" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>708</v>
       </c>
@@ -13072,8 +14182,14 @@
       <c r="P184" t="s">
         <v>710</v>
       </c>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q184" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R184" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>711</v>
       </c>
@@ -13122,8 +14238,14 @@
       <c r="P185" t="s">
         <v>713</v>
       </c>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q185" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R185" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>714</v>
       </c>
@@ -13172,8 +14294,14 @@
       <c r="P186" t="s">
         <v>716</v>
       </c>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q186" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R186" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>717</v>
       </c>
@@ -13222,8 +14350,14 @@
       <c r="P187" t="s">
         <v>720</v>
       </c>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q187" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R187" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>721</v>
       </c>
@@ -13272,8 +14406,14 @@
       <c r="P188" t="s">
         <v>723</v>
       </c>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q188" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R188" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>724</v>
       </c>
@@ -13322,8 +14462,14 @@
       <c r="P189" t="s">
         <v>726</v>
       </c>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q189" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R189" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>727</v>
       </c>
@@ -13372,8 +14518,14 @@
       <c r="P190" t="s">
         <v>729</v>
       </c>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q190" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R190" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>730</v>
       </c>
@@ -13422,8 +14574,14 @@
       <c r="P191" t="s">
         <v>733</v>
       </c>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q191" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R191" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>734</v>
       </c>
@@ -13472,8 +14630,14 @@
       <c r="P192" t="s">
         <v>737</v>
       </c>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q192" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R192" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>738</v>
       </c>
@@ -13522,8 +14686,14 @@
       <c r="P193" t="s">
         <v>740</v>
       </c>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q193" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R193" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>741</v>
       </c>
@@ -13572,8 +14742,14 @@
       <c r="P194" t="s">
         <v>743</v>
       </c>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q194" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R194" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>744</v>
       </c>
@@ -13622,8 +14798,14 @@
       <c r="P195" t="s">
         <v>746</v>
       </c>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q195" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R195" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>747</v>
       </c>
@@ -13672,8 +14854,14 @@
       <c r="P196" t="s">
         <v>749</v>
       </c>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q196" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R196" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>750</v>
       </c>
@@ -13722,8 +14910,14 @@
       <c r="P197" t="s">
         <v>752</v>
       </c>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q197" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R197" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>753</v>
       </c>
@@ -13772,8 +14966,14 @@
       <c r="P198" t="s">
         <v>755</v>
       </c>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q198" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R198" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>756</v>
       </c>
@@ -13822,8 +15022,14 @@
       <c r="P199" t="s">
         <v>758</v>
       </c>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q199" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R199" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>759</v>
       </c>
@@ -13872,8 +15078,14 @@
       <c r="P200" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q200" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R200" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>762</v>
       </c>
@@ -13922,8 +15134,14 @@
       <c r="P201" t="s">
         <v>765</v>
       </c>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q201" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R201" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>766</v>
       </c>
@@ -13972,8 +15190,14 @@
       <c r="P202" t="s">
         <v>768</v>
       </c>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q202" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R202" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>769</v>
       </c>
@@ -14022,8 +15246,14 @@
       <c r="P203" t="s">
         <v>771</v>
       </c>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q203" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R203" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>772</v>
       </c>
@@ -14072,8 +15302,14 @@
       <c r="P204" t="s">
         <v>774</v>
       </c>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q204" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R204" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>775</v>
       </c>
@@ -14122,8 +15358,14 @@
       <c r="P205" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q205" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R205" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>778</v>
       </c>
@@ -14172,8 +15414,14 @@
       <c r="P206" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q206" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R206" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>781</v>
       </c>
@@ -14222,8 +15470,14 @@
       <c r="P207" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q207" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R207" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1155</v>
       </c>
@@ -14272,8 +15526,14 @@
       <c r="P208" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q208" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R208" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1156</v>
       </c>
@@ -14322,8 +15582,14 @@
       <c r="P209" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q209" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R209" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1157</v>
       </c>
@@ -14372,8 +15638,14 @@
       <c r="P210" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q210" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R210" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1158</v>
       </c>
@@ -14422,8 +15694,14 @@
       <c r="P211" t="s">
         <v>796</v>
       </c>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q211" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R211" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>797</v>
       </c>
@@ -14472,8 +15750,14 @@
       <c r="P212" t="s">
         <v>800</v>
       </c>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q212" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R212" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>801</v>
       </c>
@@ -14522,8 +15806,14 @@
       <c r="P213" t="s">
         <v>805</v>
       </c>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q213" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R213" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>806</v>
       </c>
@@ -14572,8 +15862,14 @@
       <c r="P214" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q214" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R214" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>811</v>
       </c>
@@ -14622,8 +15918,14 @@
       <c r="P215" t="s">
         <v>814</v>
       </c>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q215" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R215" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>815</v>
       </c>
@@ -14672,8 +15974,14 @@
       <c r="P216" t="s">
         <v>817</v>
       </c>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q216" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R216" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>818</v>
       </c>
@@ -14722,8 +16030,14 @@
       <c r="P217" t="s">
         <v>821</v>
       </c>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q217" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R217" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>822</v>
       </c>
@@ -14772,8 +16086,14 @@
       <c r="P218" t="s">
         <v>824</v>
       </c>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q218" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R218" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>825</v>
       </c>
@@ -14822,8 +16142,14 @@
       <c r="P219" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q219" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R219" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>829</v>
       </c>
@@ -14872,8 +16198,14 @@
       <c r="P220" t="s">
         <v>833</v>
       </c>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q220" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R220" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>834</v>
       </c>
@@ -14922,8 +16254,14 @@
       <c r="P221" t="s">
         <v>836</v>
       </c>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q221" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R221" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>837</v>
       </c>
@@ -14972,8 +16310,14 @@
       <c r="P222" t="s">
         <v>840</v>
       </c>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q222" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R222" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>841</v>
       </c>
@@ -15022,8 +16366,14 @@
       <c r="P223" t="s">
         <v>844</v>
       </c>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q223" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R223" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>845</v>
       </c>
@@ -15072,8 +16422,14 @@
       <c r="P224" t="s">
         <v>848</v>
       </c>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q224" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R224" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>849</v>
       </c>
@@ -15122,8 +16478,14 @@
       <c r="P225" t="s">
         <v>851</v>
       </c>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q225" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R225" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>852</v>
       </c>
@@ -15172,8 +16534,14 @@
       <c r="P226" t="s">
         <v>854</v>
       </c>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q226" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R226" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>855</v>
       </c>
@@ -15222,8 +16590,14 @@
       <c r="P227" t="s">
         <v>859</v>
       </c>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q227" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R227" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>860</v>
       </c>
@@ -15272,8 +16646,14 @@
       <c r="P228" t="s">
         <v>863</v>
       </c>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q228" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R228" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>864</v>
       </c>
@@ -15322,8 +16702,14 @@
       <c r="P229" t="s">
         <v>867</v>
       </c>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q229" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R229" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>868</v>
       </c>
@@ -15372,8 +16758,14 @@
       <c r="P230" t="s">
         <v>870</v>
       </c>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q230" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R230" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>871</v>
       </c>
@@ -15422,8 +16814,14 @@
       <c r="P231" t="s">
         <v>873</v>
       </c>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q231" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R231" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>874</v>
       </c>
@@ -15472,8 +16870,14 @@
       <c r="P232" t="s">
         <v>876</v>
       </c>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q232" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R232" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>877</v>
       </c>
@@ -15522,8 +16926,14 @@
       <c r="P233" t="s">
         <v>879</v>
       </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q233" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R233" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>880</v>
       </c>
@@ -15572,8 +16982,14 @@
       <c r="P234" t="s">
         <v>884</v>
       </c>
-    </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q234" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R234" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>885</v>
       </c>
@@ -15622,8 +17038,14 @@
       <c r="P235" t="s">
         <v>888</v>
       </c>
-    </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q235" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R235" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>889</v>
       </c>
@@ -15672,8 +17094,14 @@
       <c r="P236" t="s">
         <v>891</v>
       </c>
-    </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q236" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R236" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>892</v>
       </c>
@@ -15722,8 +17150,14 @@
       <c r="P237" t="s">
         <v>894</v>
       </c>
-    </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q237" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R237" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>895</v>
       </c>
@@ -15772,8 +17206,14 @@
       <c r="P238" t="s">
         <v>897</v>
       </c>
-    </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q238" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R238" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>898</v>
       </c>
@@ -15822,8 +17262,14 @@
       <c r="P239" t="s">
         <v>901</v>
       </c>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q239" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R239" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>902</v>
       </c>
@@ -15872,8 +17318,14 @@
       <c r="P240" t="s">
         <v>904</v>
       </c>
-    </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q240" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R240" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>905</v>
       </c>
@@ -15922,8 +17374,14 @@
       <c r="P241" t="s">
         <v>907</v>
       </c>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q241" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R241" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>908</v>
       </c>
@@ -15972,8 +17430,14 @@
       <c r="P242" t="s">
         <v>910</v>
       </c>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q242" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R242" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>911</v>
       </c>
@@ -16022,8 +17486,14 @@
       <c r="P243" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q243" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R243" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1142</v>
       </c>
@@ -16072,8 +17542,14 @@
       <c r="P244" t="s">
         <v>915</v>
       </c>
-    </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q244" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R244" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1143</v>
       </c>
@@ -16122,8 +17598,14 @@
       <c r="P245" t="s">
         <v>917</v>
       </c>
-    </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q245" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R245" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1146</v>
       </c>
@@ -16172,8 +17654,14 @@
       <c r="P246" t="s">
         <v>919</v>
       </c>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q246" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R246" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1145</v>
       </c>
@@ -16222,8 +17710,14 @@
       <c r="P247" t="s">
         <v>921</v>
       </c>
-    </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q247" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R247" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1144</v>
       </c>
@@ -16272,8 +17766,14 @@
       <c r="P248" t="s">
         <v>923</v>
       </c>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q248" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R248" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>924</v>
       </c>
@@ -16322,8 +17822,14 @@
       <c r="P249" t="s">
         <v>926</v>
       </c>
-    </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q249" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R249" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>927</v>
       </c>
@@ -16372,8 +17878,14 @@
       <c r="P250" t="s">
         <v>929</v>
       </c>
-    </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q250" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R250" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>930</v>
       </c>
@@ -16422,8 +17934,14 @@
       <c r="P251" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q251" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R251" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>933</v>
       </c>
@@ -16472,8 +17990,14 @@
       <c r="P252" t="s">
         <v>935</v>
       </c>
-    </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q252" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R252" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>936</v>
       </c>
@@ -16522,8 +18046,14 @@
       <c r="P253" t="s">
         <v>938</v>
       </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q253" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R253" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>939</v>
       </c>
@@ -16572,8 +18102,14 @@
       <c r="P254" t="s">
         <v>941</v>
       </c>
-    </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q254" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R254" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>942</v>
       </c>
@@ -16622,8 +18158,14 @@
       <c r="P255" t="s">
         <v>944</v>
       </c>
-    </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q255" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R255" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>945</v>
       </c>
@@ -16672,8 +18214,14 @@
       <c r="P256" t="s">
         <v>947</v>
       </c>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q256" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R256" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>949</v>
       </c>
@@ -16722,8 +18270,14 @@
       <c r="P257" t="s">
         <v>951</v>
       </c>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q257" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R257" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>952</v>
       </c>
@@ -16772,8 +18326,14 @@
       <c r="P258" t="s">
         <v>956</v>
       </c>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q258" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R258" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>957</v>
       </c>
@@ -16822,8 +18382,14 @@
       <c r="P259" t="s">
         <v>960</v>
       </c>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q259" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R259" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>961</v>
       </c>
@@ -16872,8 +18438,14 @@
       <c r="P260" t="s">
         <v>965</v>
       </c>
-    </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q260" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R260" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>966</v>
       </c>
@@ -16922,8 +18494,14 @@
       <c r="P261" t="s">
         <v>969</v>
       </c>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q261" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R261" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>970</v>
       </c>
@@ -16972,8 +18550,14 @@
       <c r="P262" t="s">
         <v>975</v>
       </c>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q262" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R262" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>976</v>
       </c>
@@ -17022,8 +18606,14 @@
       <c r="P263" t="s">
         <v>978</v>
       </c>
-    </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q263" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R263" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>979</v>
       </c>
@@ -17072,8 +18662,14 @@
       <c r="P264" t="s">
         <v>982</v>
       </c>
-    </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q264" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R264" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>983</v>
       </c>
@@ -17122,8 +18718,14 @@
       <c r="P265" t="s">
         <v>987</v>
       </c>
-    </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q265" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R265" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>988</v>
       </c>
@@ -17172,8 +18774,14 @@
       <c r="P266" t="s">
         <v>992</v>
       </c>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q266" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R266" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>993</v>
       </c>
@@ -17222,8 +18830,14 @@
       <c r="P267" t="s">
         <v>995</v>
       </c>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q267" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R267" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>996</v>
       </c>
@@ -17272,8 +18886,14 @@
       <c r="P268" t="s">
         <v>998</v>
       </c>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q268" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R268" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>999</v>
       </c>
@@ -17322,8 +18942,14 @@
       <c r="P269" t="s">
         <v>1001</v>
       </c>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q269" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R269" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1002</v>
       </c>
@@ -17372,8 +18998,14 @@
       <c r="P270" t="s">
         <v>1004</v>
       </c>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q270" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R270" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1005</v>
       </c>
@@ -17422,8 +19054,14 @@
       <c r="P271" t="s">
         <v>1008</v>
       </c>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q271" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R271" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1009</v>
       </c>
@@ -17472,8 +19110,14 @@
       <c r="P272" t="s">
         <v>1011</v>
       </c>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q272" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R272" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1012</v>
       </c>
@@ -17522,8 +19166,14 @@
       <c r="P273" t="s">
         <v>1015</v>
       </c>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q273" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R273" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1016</v>
       </c>
@@ -17572,8 +19222,14 @@
       <c r="P274" t="s">
         <v>1018</v>
       </c>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q274" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R274" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1019</v>
       </c>
@@ -17622,8 +19278,14 @@
       <c r="P275" t="s">
         <v>1021</v>
       </c>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q275" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R275" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1022</v>
       </c>
@@ -17672,8 +19334,14 @@
       <c r="P276" t="s">
         <v>1024</v>
       </c>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q276" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R276" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1025</v>
       </c>
@@ -17722,8 +19390,14 @@
       <c r="P277" t="s">
         <v>1028</v>
       </c>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q277" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R277" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1029</v>
       </c>
@@ -17772,8 +19446,14 @@
       <c r="P278" t="s">
         <v>1031</v>
       </c>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q278" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R278" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1032</v>
       </c>
@@ -17822,8 +19502,14 @@
       <c r="P279" t="s">
         <v>1034</v>
       </c>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q279" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R279" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1035</v>
       </c>
@@ -17872,8 +19558,14 @@
       <c r="P280" t="s">
         <v>1037</v>
       </c>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q280" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R280" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1038</v>
       </c>
@@ -17922,8 +19614,14 @@
       <c r="P281" t="s">
         <v>1040</v>
       </c>
-    </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q281" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R281" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1041</v>
       </c>
@@ -17972,8 +19670,14 @@
       <c r="P282" t="s">
         <v>1043</v>
       </c>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q282" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R282" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1044</v>
       </c>
@@ -18022,8 +19726,14 @@
       <c r="P283" t="s">
         <v>1046</v>
       </c>
-    </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q283" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R283" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1047</v>
       </c>
@@ -18072,8 +19782,14 @@
       <c r="P284" t="s">
         <v>1049</v>
       </c>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q284" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R284" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1050</v>
       </c>
@@ -18122,8 +19838,14 @@
       <c r="P285" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q285" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R285" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1053</v>
       </c>
@@ -18172,8 +19894,14 @@
       <c r="P286" t="s">
         <v>1055</v>
       </c>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q286" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R286" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1056</v>
       </c>
@@ -18222,8 +19950,14 @@
       <c r="P287" t="s">
         <v>1058</v>
       </c>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q287" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R287" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1059</v>
       </c>
@@ -18272,8 +20006,14 @@
       <c r="P288" t="s">
         <v>1061</v>
       </c>
-    </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q288" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R288" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1159</v>
       </c>
@@ -18322,8 +20062,14 @@
       <c r="P289" t="s">
         <v>1064</v>
       </c>
-    </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q289" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R289" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1065</v>
       </c>
@@ -18372,8 +20118,14 @@
       <c r="P290" t="s">
         <v>1067</v>
       </c>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q290" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R290" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1068</v>
       </c>
@@ -18422,8 +20174,14 @@
       <c r="P291" t="s">
         <v>1070</v>
       </c>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q291" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R291" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1071</v>
       </c>
@@ -18472,8 +20230,14 @@
       <c r="P292" t="s">
         <v>1073</v>
       </c>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q292" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R292" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1074</v>
       </c>
@@ -18522,8 +20286,14 @@
       <c r="P293" t="s">
         <v>1076</v>
       </c>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q293" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R293" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1077</v>
       </c>
@@ -18572,8 +20342,14 @@
       <c r="P294" t="s">
         <v>1079</v>
       </c>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q294" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R294" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1080</v>
       </c>
@@ -18622,8 +20398,14 @@
       <c r="P295" t="s">
         <v>1082</v>
       </c>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q295" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R295" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1083</v>
       </c>
@@ -18672,8 +20454,14 @@
       <c r="P296" t="s">
         <v>1085</v>
       </c>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q296" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R296" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1086</v>
       </c>
@@ -18722,8 +20510,14 @@
       <c r="P297" t="s">
         <v>1088</v>
       </c>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q297" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R297" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1089</v>
       </c>
@@ -18772,8 +20566,14 @@
       <c r="P298" t="s">
         <v>1091</v>
       </c>
-    </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q298" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R298" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1092</v>
       </c>
@@ -18822,8 +20622,14 @@
       <c r="P299" t="s">
         <v>1095</v>
       </c>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q299" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R299" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1096</v>
       </c>
@@ -18872,8 +20678,14 @@
       <c r="P300" t="s">
         <v>1099</v>
       </c>
-    </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q300" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R300" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1100</v>
       </c>
@@ -18922,8 +20734,14 @@
       <c r="P301" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q301" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R301" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1103</v>
       </c>
@@ -18972,8 +20790,14 @@
       <c r="P302" t="s">
         <v>1105</v>
       </c>
-    </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q302" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R302" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1106</v>
       </c>
@@ -19022,8 +20846,14 @@
       <c r="P303" t="s">
         <v>1108</v>
       </c>
-    </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q303" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R303" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1109</v>
       </c>
@@ -19072,8 +20902,14 @@
       <c r="P304" t="s">
         <v>1111</v>
       </c>
-    </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q304" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R304" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1112</v>
       </c>
@@ -19122,8 +20958,14 @@
       <c r="P305" t="s">
         <v>1115</v>
       </c>
-    </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q305" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R305" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1116</v>
       </c>
@@ -19172,8 +21014,14 @@
       <c r="P306" t="s">
         <v>1118</v>
       </c>
-    </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q306" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R306" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1119</v>
       </c>
@@ -19222,8 +21070,14 @@
       <c r="P307" t="s">
         <v>1121</v>
       </c>
-    </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q307" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R307" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1122</v>
       </c>
@@ -19272,8 +21126,14 @@
       <c r="P308" t="s">
         <v>1124</v>
       </c>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q308" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R308" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1125</v>
       </c>
@@ -19322,8 +21182,14 @@
       <c r="P309" t="s">
         <v>1127</v>
       </c>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q309" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R309" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1128</v>
       </c>
@@ -19372,8 +21238,14 @@
       <c r="P310" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q310" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R310" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1131</v>
       </c>
@@ -19421,6 +21293,12 @@
       </c>
       <c r="P311" t="s">
         <v>1133</v>
+      </c>
+      <c r="Q311" t="s">
+        <v>1170</v>
+      </c>
+      <c r="R311" t="s">
+        <v>1170</v>
       </c>
     </row>
   </sheetData>

--- a/RemasterShips/ship_data_Extract.xlsx
+++ b/RemasterShips/ship_data_Extract.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\RemasterShips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBF507A-8CDE-4CE2-8DF1-6081599008CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043384A8-8C16-4F51-BA73-FB35A9AFC40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4961" uniqueCount="1169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4971" uniqueCount="1179">
   <si>
     <t>Name</t>
   </si>
@@ -3543,6 +3543,36 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Princess Liner_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Princess Liner_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Affluence Liner_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Affluence Liner_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/L-Type Barge_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/L-Type Barge_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Nirvana_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Nirvana_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Precedentone_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Precedentone_CardFrontImage.png</t>
   </si>
 </sst>
 </file>
@@ -3992,11 +4022,26 @@
       <c r="D2">
         <v>20</v>
       </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
       <c r="I2">
         <v>4</v>
       </c>
       <c r="J2">
         <v>4</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
       </c>
       <c r="L2" t="s">
         <v>17</v>
@@ -6936,6 +6981,9 @@
       <c r="A55" t="s">
         <v>242</v>
       </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
       <c r="C55" t="s">
         <v>243</v>
       </c>
@@ -6972,13 +7020,11 @@
       <c r="N55" t="s">
         <v>241</v>
       </c>
-      <c r="O55" t="str">
-        <f>_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/",$A55,"_ModelImage.png")</f>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Princess Liner_ModelImage.png</v>
-      </c>
-      <c r="P55" t="str">
-        <f>_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/",$A55,"_CardFrontImage.png")</f>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Princess Liner_CardFrontImage.png</v>
+      <c r="O55" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>1170</v>
       </c>
       <c r="Q55" t="s">
         <v>1168</v>
@@ -6991,6 +7037,9 @@
       <c r="A56" t="s">
         <v>245</v>
       </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
       <c r="C56" t="s">
         <v>243</v>
       </c>
@@ -7027,13 +7076,11 @@
       <c r="N56" t="s">
         <v>241</v>
       </c>
-      <c r="O56" t="str">
-        <f t="shared" ref="O56:O59" si="0">_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/",A56,"_ModelImage.png")</f>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Affluence Liner_ModelImage.png</v>
-      </c>
-      <c r="P56" t="str">
-        <f t="shared" ref="P56:P59" si="1">_xlfn.CONCAT("https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/",$A56,"_CardFrontImage.png")</f>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Affluence Liner_CardFrontImage.png</v>
+      <c r="O56" s="2" t="s">
+        <v>1171</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>1172</v>
       </c>
       <c r="Q56" t="s">
         <v>1168</v>
@@ -7046,6 +7093,9 @@
       <c r="A57" t="s">
         <v>247</v>
       </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
       <c r="C57" t="s">
         <v>248</v>
       </c>
@@ -7082,13 +7132,11 @@
       <c r="N57" t="s">
         <v>241</v>
       </c>
-      <c r="O57" t="str">
-        <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/L-Type Barge_ModelImage.png</v>
-      </c>
-      <c r="P57" t="str">
-        <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/L-Type Barge_CardFrontImage.png</v>
+      <c r="O57" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>1174</v>
       </c>
       <c r="Q57" t="s">
         <v>1168</v>
@@ -7101,6 +7149,9 @@
       <c r="A58" t="s">
         <v>250</v>
       </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
       <c r="C58" t="s">
         <v>251</v>
       </c>
@@ -7137,13 +7188,11 @@
       <c r="N58" t="s">
         <v>241</v>
       </c>
-      <c r="O58" t="str">
-        <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Nirvana_ModelImage.png</v>
-      </c>
-      <c r="P58" t="str">
-        <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Nirvana_CardFrontImage.png</v>
+      <c r="O58" s="2" t="s">
+        <v>1175</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>1176</v>
       </c>
       <c r="Q58" t="s">
         <v>1168</v>
@@ -7156,6 +7205,9 @@
       <c r="A59" t="s">
         <v>253</v>
       </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
       <c r="C59" t="s">
         <v>254</v>
       </c>
@@ -7192,13 +7244,11 @@
       <c r="N59" t="s">
         <v>241</v>
       </c>
-      <c r="O59" t="str">
-        <f t="shared" si="0"/>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Precedent One_ModelImage.png</v>
-      </c>
-      <c r="P59" t="str">
-        <f t="shared" si="1"/>
-        <v>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Precedent One_CardFrontImage.png</v>
+      <c r="O59" s="2" t="s">
+        <v>1177</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>1178</v>
       </c>
       <c r="Q59" t="s">
         <v>1168</v>
@@ -21339,6 +21389,16 @@
     <hyperlink ref="O210" r:id="rId15" xr:uid="{95162EE6-250A-4CB3-A94B-494506141FB6}"/>
     <hyperlink ref="O211" r:id="rId16" xr:uid="{6498D032-A8E8-409E-BDCA-3C64D617B30B}"/>
     <hyperlink ref="O289" r:id="rId17" xr:uid="{1050127A-DA53-44A9-B236-8F59FDC951C4}"/>
+    <hyperlink ref="P55" r:id="rId18" xr:uid="{F7AC5C65-132A-4F7B-A7E1-25A0A8BFEE94}"/>
+    <hyperlink ref="O57" r:id="rId19" xr:uid="{15ABFBD9-AAA3-4116-AA97-4FCC21B8A01E}"/>
+    <hyperlink ref="P57" r:id="rId20" xr:uid="{ED4C8F0D-748A-4A4C-9C0D-71B2F0F2AFC2}"/>
+    <hyperlink ref="O55" r:id="rId21" xr:uid="{65F8166B-EC53-41A0-9456-A49CD7D538E4}"/>
+    <hyperlink ref="P56" r:id="rId22" xr:uid="{007FED3A-FBA2-4D9E-A9D2-1C2F00014916}"/>
+    <hyperlink ref="O56" r:id="rId23" xr:uid="{18A1F500-5FFC-434B-A9D8-393F63879187}"/>
+    <hyperlink ref="P59" r:id="rId24" xr:uid="{5C3597F8-CAB0-47C0-9EAD-5F3944EF7A35}"/>
+    <hyperlink ref="O59" r:id="rId25" xr:uid="{14E0A252-D05E-4F48-992A-C281B6D05FFC}"/>
+    <hyperlink ref="P58" r:id="rId26" xr:uid="{0A0D9651-9D13-4DAB-A1D7-F138773A60F7}"/>
+    <hyperlink ref="O58" r:id="rId27" xr:uid="{48D462A0-3134-48DE-AD12-1BB27C9D5DEB}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/RemasterShips/ship_data_Extract.xlsx
+++ b/RemasterShips/ship_data_Extract.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\RemasterShips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{043384A8-8C16-4F51-BA73-FB35A9AFC40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB48104F-E04C-4493-BA03-F40ECDBF3504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="1500" windowWidth="27435" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ship Data'!$A$1:$P$311</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ship Data'!$A$1:$P$312</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4971" uniqueCount="1179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="1181">
   <si>
     <t>Name</t>
   </si>
@@ -3573,6 +3573,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Precedentone_CardFrontImage.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pungari Thresher </t>
+  </si>
+  <si>
+    <t>Hive Ship</t>
   </si>
 </sst>
 </file>
@@ -3932,7 +3938,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R311"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:R312"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="1"/>
@@ -4009,7 +4016,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1164</v>
       </c>
@@ -4065,7 +4072,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -4121,7 +4128,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>32</v>
       </c>
@@ -4177,7 +4184,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -4233,7 +4240,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -4289,7 +4296,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>54</v>
       </c>
@@ -4345,7 +4352,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>62</v>
       </c>
@@ -4401,7 +4408,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>66</v>
       </c>
@@ -4457,7 +4464,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -4513,7 +4520,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -4569,7 +4576,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -4625,7 +4632,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>82</v>
       </c>
@@ -4681,7 +4688,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -4737,7 +4744,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -4793,7 +4800,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>101</v>
       </c>
@@ -4849,7 +4856,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>104</v>
       </c>
@@ -4905,7 +4912,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>109</v>
       </c>
@@ -4961,7 +4968,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -5017,7 +5024,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -5073,7 +5080,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>120</v>
       </c>
@@ -5129,7 +5136,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>124</v>
       </c>
@@ -5185,7 +5192,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -5241,7 +5248,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -5297,7 +5304,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>135</v>
       </c>
@@ -5353,7 +5360,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>138</v>
       </c>
@@ -5409,7 +5416,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>142</v>
       </c>
@@ -5465,7 +5472,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -5521,7 +5528,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>149</v>
       </c>
@@ -5577,7 +5584,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>153</v>
       </c>
@@ -5633,7 +5640,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>156</v>
       </c>
@@ -5689,7 +5696,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>160</v>
       </c>
@@ -5745,7 +5752,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -5801,7 +5808,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>167</v>
       </c>
@@ -5857,7 +5864,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>170</v>
       </c>
@@ -5913,7 +5920,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>174</v>
       </c>
@@ -5969,7 +5976,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>177</v>
       </c>
@@ -6025,7 +6032,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>180</v>
       </c>
@@ -6081,7 +6088,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -6137,7 +6144,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>188</v>
       </c>
@@ -6193,7 +6200,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>192</v>
       </c>
@@ -6249,7 +6256,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>195</v>
       </c>
@@ -6305,7 +6312,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>198</v>
       </c>
@@ -6361,7 +6368,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>201</v>
       </c>
@@ -6417,7 +6424,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>205</v>
       </c>
@@ -6473,7 +6480,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>208</v>
       </c>
@@ -6529,7 +6536,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>211</v>
       </c>
@@ -6585,7 +6592,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>215</v>
       </c>
@@ -6641,7 +6648,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>218</v>
       </c>
@@ -6697,7 +6704,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>221</v>
       </c>
@@ -6753,7 +6760,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>227</v>
       </c>
@@ -6809,7 +6816,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>230</v>
       </c>
@@ -6865,7 +6872,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>233</v>
       </c>
@@ -6921,7 +6928,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>238</v>
       </c>
@@ -6977,7 +6984,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>242</v>
       </c>
@@ -7033,7 +7040,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>245</v>
       </c>
@@ -7089,7 +7096,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>247</v>
       </c>
@@ -7145,7 +7152,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>250</v>
       </c>
@@ -7201,7 +7208,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>253</v>
       </c>
@@ -7257,7 +7264,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>256</v>
       </c>
@@ -7313,7 +7320,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>260</v>
       </c>
@@ -7369,7 +7376,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>264</v>
       </c>
@@ -7425,7 +7432,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>269</v>
       </c>
@@ -7481,7 +7488,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>274</v>
       </c>
@@ -7537,7 +7544,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>279</v>
       </c>
@@ -7593,7 +7600,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>284</v>
       </c>
@@ -7649,7 +7656,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>289</v>
       </c>
@@ -7705,7 +7712,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>295</v>
       </c>
@@ -7761,7 +7768,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>1132</v>
       </c>
@@ -7817,7 +7824,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1133</v>
       </c>
@@ -7873,7 +7880,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>1134</v>
       </c>
@@ -7929,7 +7936,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1135</v>
       </c>
@@ -7985,7 +7992,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>315</v>
       </c>
@@ -8041,7 +8048,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>319</v>
       </c>
@@ -8097,7 +8104,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>323</v>
       </c>
@@ -8153,7 +8160,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>327</v>
       </c>
@@ -8209,7 +8216,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>330</v>
       </c>
@@ -8265,7 +8272,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>333</v>
       </c>
@@ -8321,7 +8328,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>338</v>
       </c>
@@ -8377,7 +8384,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>342</v>
       </c>
@@ -8433,7 +8440,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>345</v>
       </c>
@@ -8489,7 +8496,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>350</v>
       </c>
@@ -8545,7 +8552,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>354</v>
       </c>
@@ -8601,7 +8608,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>359</v>
       </c>
@@ -8657,7 +8664,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>364</v>
       </c>
@@ -8713,7 +8720,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>368</v>
       </c>
@@ -8769,7 +8776,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>371</v>
       </c>
@@ -8825,7 +8832,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>374</v>
       </c>
@@ -8881,7 +8888,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>377</v>
       </c>
@@ -8937,7 +8944,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>381</v>
       </c>
@@ -8993,7 +9000,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>384</v>
       </c>
@@ -9049,7 +9056,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>387</v>
       </c>
@@ -9105,7 +9112,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>390</v>
       </c>
@@ -9161,7 +9168,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>393</v>
       </c>
@@ -9217,7 +9224,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>396</v>
       </c>
@@ -9273,7 +9280,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>399</v>
       </c>
@@ -9329,7 +9336,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>402</v>
       </c>
@@ -9385,7 +9392,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>406</v>
       </c>
@@ -9441,7 +9448,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>409</v>
       </c>
@@ -9497,7 +9504,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>412</v>
       </c>
@@ -9553,7 +9560,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>415</v>
       </c>
@@ -9609,7 +9616,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>418</v>
       </c>
@@ -9665,7 +9672,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>422</v>
       </c>
@@ -9721,7 +9728,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>426</v>
       </c>
@@ -9777,7 +9784,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>429</v>
       </c>
@@ -9833,7 +9840,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>432</v>
       </c>
@@ -9889,7 +9896,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>435</v>
       </c>
@@ -9945,7 +9952,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>438</v>
       </c>
@@ -10001,7 +10008,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>441</v>
       </c>
@@ -10057,7 +10064,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>444</v>
       </c>
@@ -10113,7 +10120,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>447</v>
       </c>
@@ -10169,7 +10176,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>450</v>
       </c>
@@ -10225,7 +10232,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>453</v>
       </c>
@@ -10281,7 +10288,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>456</v>
       </c>
@@ -10337,7 +10344,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>459</v>
       </c>
@@ -10393,7 +10400,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>463</v>
       </c>
@@ -10449,7 +10456,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>467</v>
       </c>
@@ -10505,7 +10512,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>470</v>
       </c>
@@ -10561,7 +10568,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>473</v>
       </c>
@@ -10617,7 +10624,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>476</v>
       </c>
@@ -10673,7 +10680,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>479</v>
       </c>
@@ -10729,7 +10736,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1145</v>
       </c>
@@ -10785,7 +10792,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1146</v>
       </c>
@@ -10841,7 +10848,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>1147</v>
       </c>
@@ -10897,7 +10904,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>1148</v>
       </c>
@@ -10953,7 +10960,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>496</v>
       </c>
@@ -11009,7 +11016,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>499</v>
       </c>
@@ -11065,7 +11072,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>339</v>
       </c>
@@ -11121,7 +11128,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>97</v>
       </c>
@@ -11177,7 +11184,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>510</v>
       </c>
@@ -11233,7 +11240,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>514</v>
       </c>
@@ -11289,7 +11296,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>519</v>
       </c>
@@ -11345,7 +11352,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>524</v>
       </c>
@@ -11401,7 +11408,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>528</v>
       </c>
@@ -11457,7 +11464,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>533</v>
       </c>
@@ -11513,7 +11520,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>536</v>
       </c>
@@ -11569,7 +11576,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>541</v>
       </c>
@@ -11625,7 +11632,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>150</v>
       </c>
@@ -11681,7 +11688,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>161</v>
       </c>
@@ -11737,7 +11744,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>189</v>
       </c>
@@ -11793,7 +11800,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>555</v>
       </c>
@@ -11849,7 +11856,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>559</v>
       </c>
@@ -11905,7 +11912,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>562</v>
       </c>
@@ -11961,7 +11968,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>565</v>
       </c>
@@ -12017,7 +12024,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>570</v>
       </c>
@@ -12073,7 +12080,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>573</v>
       </c>
@@ -12129,7 +12136,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>576</v>
       </c>
@@ -12185,7 +12192,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>580</v>
       </c>
@@ -12241,7 +12248,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>584</v>
       </c>
@@ -12297,7 +12304,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>587</v>
       </c>
@@ -12353,7 +12360,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>590</v>
       </c>
@@ -12409,7 +12416,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>594</v>
       </c>
@@ -12465,7 +12472,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>597</v>
       </c>
@@ -12521,7 +12528,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>601</v>
       </c>
@@ -12577,7 +12584,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>604</v>
       </c>
@@ -12633,7 +12640,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>607</v>
       </c>
@@ -12689,7 +12696,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>610</v>
       </c>
@@ -12745,7 +12752,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>613</v>
       </c>
@@ -12801,7 +12808,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>617</v>
       </c>
@@ -12857,7 +12864,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>622</v>
       </c>
@@ -12913,7 +12920,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>1149</v>
       </c>
@@ -12969,7 +12976,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1150</v>
       </c>
@@ -13025,7 +13032,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>1151</v>
       </c>
@@ -13081,7 +13088,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>1152</v>
       </c>
@@ -13137,7 +13144,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>640</v>
       </c>
@@ -13193,7 +13200,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>644</v>
       </c>
@@ -13249,7 +13256,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>649</v>
       </c>
@@ -13305,7 +13312,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>654</v>
       </c>
@@ -13361,7 +13368,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>657</v>
       </c>
@@ -13417,7 +13424,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>660</v>
       </c>
@@ -13473,7 +13480,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>663</v>
       </c>
@@ -13529,7 +13536,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>666</v>
       </c>
@@ -13585,7 +13592,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>669</v>
       </c>
@@ -13641,7 +13648,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>673</v>
       </c>
@@ -13697,7 +13704,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>677</v>
       </c>
@@ -13753,7 +13760,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>680</v>
       </c>
@@ -13809,7 +13816,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>683</v>
       </c>
@@ -13865,7 +13872,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>688</v>
       </c>
@@ -13921,7 +13928,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>691</v>
       </c>
@@ -13977,7 +13984,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>694</v>
       </c>
@@ -14033,7 +14040,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>697</v>
       </c>
@@ -14089,7 +14096,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>700</v>
       </c>
@@ -14145,7 +14152,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>703</v>
       </c>
@@ -14201,7 +14208,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>706</v>
       </c>
@@ -14257,7 +14264,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>709</v>
       </c>
@@ -14313,7 +14320,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>712</v>
       </c>
@@ -14369,7 +14376,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>715</v>
       </c>
@@ -14425,7 +14432,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>719</v>
       </c>
@@ -14481,7 +14488,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>722</v>
       </c>
@@ -14537,7 +14544,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>725</v>
       </c>
@@ -14593,7 +14600,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>728</v>
       </c>
@@ -14649,7 +14656,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>732</v>
       </c>
@@ -14705,7 +14712,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>736</v>
       </c>
@@ -14761,7 +14768,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>739</v>
       </c>
@@ -14817,7 +14824,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>742</v>
       </c>
@@ -14873,7 +14880,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>745</v>
       </c>
@@ -14929,7 +14936,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>748</v>
       </c>
@@ -14985,7 +14992,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>751</v>
       </c>
@@ -15041,7 +15048,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>754</v>
       </c>
@@ -15097,7 +15104,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>757</v>
       </c>
@@ -15153,7 +15160,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>760</v>
       </c>
@@ -15209,7 +15216,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>764</v>
       </c>
@@ -15265,7 +15272,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>767</v>
       </c>
@@ -15321,7 +15328,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>770</v>
       </c>
@@ -15377,7 +15384,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>773</v>
       </c>
@@ -15433,7 +15440,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>776</v>
       </c>
@@ -15489,7 +15496,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>779</v>
       </c>
@@ -15545,7 +15552,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1153</v>
       </c>
@@ -15601,7 +15608,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1154</v>
       </c>
@@ -15657,7 +15664,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1155</v>
       </c>
@@ -15713,7 +15720,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1156</v>
       </c>
@@ -15769,7 +15776,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>795</v>
       </c>
@@ -15825,7 +15832,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>799</v>
       </c>
@@ -15881,7 +15888,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>804</v>
       </c>
@@ -15937,7 +15944,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>809</v>
       </c>
@@ -15993,7 +16000,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>813</v>
       </c>
@@ -16049,7 +16056,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>816</v>
       </c>
@@ -16105,7 +16112,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>820</v>
       </c>
@@ -16161,7 +16168,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>823</v>
       </c>
@@ -16217,7 +16224,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>827</v>
       </c>
@@ -16273,7 +16280,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>832</v>
       </c>
@@ -16329,7 +16336,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>835</v>
       </c>
@@ -16385,7 +16392,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>839</v>
       </c>
@@ -16441,7 +16448,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>843</v>
       </c>
@@ -16497,7 +16504,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>847</v>
       </c>
@@ -16553,7 +16560,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>850</v>
       </c>
@@ -16609,7 +16616,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>853</v>
       </c>
@@ -16665,7 +16672,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>858</v>
       </c>
@@ -16721,7 +16728,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>862</v>
       </c>
@@ -16777,7 +16784,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>866</v>
       </c>
@@ -16833,7 +16840,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>869</v>
       </c>
@@ -16889,7 +16896,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>872</v>
       </c>
@@ -16945,7 +16952,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>875</v>
       </c>
@@ -17001,7 +17008,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>878</v>
       </c>
@@ -17057,7 +17064,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>883</v>
       </c>
@@ -17113,7 +17120,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>887</v>
       </c>
@@ -17169,7 +17176,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>890</v>
       </c>
@@ -17225,7 +17232,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>893</v>
       </c>
@@ -17281,7 +17288,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>896</v>
       </c>
@@ -17337,7 +17344,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>900</v>
       </c>
@@ -17393,7 +17400,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>903</v>
       </c>
@@ -17449,7 +17456,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>906</v>
       </c>
@@ -17505,7 +17512,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>909</v>
       </c>
@@ -17561,7 +17568,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1140</v>
       </c>
@@ -17617,7 +17624,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1141</v>
       </c>
@@ -17673,7 +17680,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1144</v>
       </c>
@@ -17729,7 +17736,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1143</v>
       </c>
@@ -17785,7 +17792,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1142</v>
       </c>
@@ -17841,7 +17848,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>922</v>
       </c>
@@ -17897,7 +17904,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>925</v>
       </c>
@@ -17953,7 +17960,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>928</v>
       </c>
@@ -18009,7 +18016,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>931</v>
       </c>
@@ -18065,7 +18072,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>934</v>
       </c>
@@ -18121,7 +18128,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>937</v>
       </c>
@@ -18177,7 +18184,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>940</v>
       </c>
@@ -18233,7 +18240,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>943</v>
       </c>
@@ -18289,7 +18296,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>947</v>
       </c>
@@ -18345,7 +18352,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>950</v>
       </c>
@@ -18401,7 +18408,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>955</v>
       </c>
@@ -18457,7 +18464,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>959</v>
       </c>
@@ -18513,7 +18520,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>964</v>
       </c>
@@ -18569,7 +18576,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>968</v>
       </c>
@@ -18625,7 +18632,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>974</v>
       </c>
@@ -18681,7 +18688,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>977</v>
       </c>
@@ -18737,7 +18744,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>981</v>
       </c>
@@ -18793,7 +18800,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>986</v>
       </c>
@@ -18849,7 +18856,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>991</v>
       </c>
@@ -18905,7 +18912,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>994</v>
       </c>
@@ -18961,7 +18968,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>997</v>
       </c>
@@ -19017,7 +19024,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1000</v>
       </c>
@@ -19073,7 +19080,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1003</v>
       </c>
@@ -19129,7 +19136,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1007</v>
       </c>
@@ -19185,7 +19192,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1010</v>
       </c>
@@ -19241,7 +19248,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1014</v>
       </c>
@@ -19297,7 +19304,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1017</v>
       </c>
@@ -19353,7 +19360,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1020</v>
       </c>
@@ -19409,7 +19416,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1023</v>
       </c>
@@ -19465,7 +19472,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1027</v>
       </c>
@@ -19521,7 +19528,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1030</v>
       </c>
@@ -19577,7 +19584,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1033</v>
       </c>
@@ -19633,7 +19640,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1036</v>
       </c>
@@ -19689,7 +19696,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1039</v>
       </c>
@@ -19745,7 +19752,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1042</v>
       </c>
@@ -19801,7 +19808,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1045</v>
       </c>
@@ -19857,7 +19864,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1048</v>
       </c>
@@ -19913,7 +19920,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1051</v>
       </c>
@@ -19969,7 +19976,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1054</v>
       </c>
@@ -20025,7 +20032,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1057</v>
       </c>
@@ -20081,7 +20088,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1157</v>
       </c>
@@ -20137,7 +20144,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1063</v>
       </c>
@@ -20193,7 +20200,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1066</v>
       </c>
@@ -20249,7 +20256,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1069</v>
       </c>
@@ -20305,7 +20312,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1072</v>
       </c>
@@ -20361,7 +20368,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1075</v>
       </c>
@@ -20417,7 +20424,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1078</v>
       </c>
@@ -20473,7 +20480,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1081</v>
       </c>
@@ -20529,7 +20536,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>1084</v>
       </c>
@@ -20585,7 +20592,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1087</v>
       </c>
@@ -20641,7 +20648,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1090</v>
       </c>
@@ -20697,7 +20704,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1094</v>
       </c>
@@ -20753,7 +20760,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1098</v>
       </c>
@@ -20809,7 +20816,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1101</v>
       </c>
@@ -20865,7 +20872,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1104</v>
       </c>
@@ -20921,7 +20928,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1107</v>
       </c>
@@ -20977,7 +20984,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1110</v>
       </c>
@@ -21033,7 +21040,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1114</v>
       </c>
@@ -21089,7 +21096,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1117</v>
       </c>
@@ -21145,7 +21152,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1120</v>
       </c>
@@ -21201,7 +21208,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1123</v>
       </c>
@@ -21257,7 +21264,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1126</v>
       </c>
@@ -21313,7 +21320,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1129</v>
       </c>
@@ -21369,8 +21376,58 @@
         <v>1168</v>
       </c>
     </row>
+    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B312">
+        <v>170</v>
+      </c>
+      <c r="C312" t="s">
+        <v>1180</v>
+      </c>
+      <c r="D312">
+        <v>40</v>
+      </c>
+      <c r="E312">
+        <v>6</v>
+      </c>
+      <c r="F312">
+        <v>4</v>
+      </c>
+      <c r="G312">
+        <v>4</v>
+      </c>
+      <c r="H312">
+        <v>14</v>
+      </c>
+      <c r="I312">
+        <v>3</v>
+      </c>
+      <c r="J312">
+        <v>5</v>
+      </c>
+      <c r="K312">
+        <v>6</v>
+      </c>
+      <c r="L312">
+        <v>1</v>
+      </c>
+      <c r="M312" t="s">
+        <v>93</v>
+      </c>
+      <c r="N312" t="s">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P311" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P312" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Hive Ship"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="O69" r:id="rId1" xr:uid="{199D85C6-8205-44AF-8889-1D194BB490BD}"/>
     <hyperlink ref="O70" r:id="rId2" xr:uid="{4C94DFDA-489B-476E-8AC6-E7F89E79353B}"/>

--- a/RemasterShips/ship_data_Extract.xlsx
+++ b/RemasterShips/ship_data_Extract.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DropFleetTTS_Repo\DropfleetTTS\RemasterShips\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB48104F-E04C-4493-BA03-F40ECDBF3504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A7BD43-9AB9-4063-911A-9774EB073025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="1500" windowWidth="27435" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39750" yWindow="1050" windowWidth="27435" windowHeight="19245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ship Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4975" uniqueCount="1181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4977" uniqueCount="1183">
   <si>
     <t>Name</t>
   </si>
@@ -3579,6 +3579,12 @@
   </si>
   <si>
     <t>Hive Ship</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Pungari Thresher_ModelImage.png</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/TemporalDistoriton/DropfleetTTS/main/RemasterShips/CIV/Pungari Thresher_CardFrontImage.png</t>
   </si>
 </sst>
 </file>
@@ -21419,6 +21425,12 @@
       <c r="N312" t="s">
         <v>241</v>
       </c>
+      <c r="O312" s="2" t="s">
+        <v>1181</v>
+      </c>
+      <c r="P312" s="2" t="s">
+        <v>1182</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P312" xr:uid="{00000000-0001-0000-0000-000000000000}">
@@ -21456,6 +21468,8 @@
     <hyperlink ref="O59" r:id="rId25" xr:uid="{14E0A252-D05E-4F48-992A-C281B6D05FFC}"/>
     <hyperlink ref="P58" r:id="rId26" xr:uid="{0A0D9651-9D13-4DAB-A1D7-F138773A60F7}"/>
     <hyperlink ref="O58" r:id="rId27" xr:uid="{48D462A0-3134-48DE-AD12-1BB27C9D5DEB}"/>
+    <hyperlink ref="O312" r:id="rId28" xr:uid="{DEF7037B-F289-4CE9-9E55-AD3BBE4D1DE8}"/>
+    <hyperlink ref="P312" r:id="rId29" xr:uid="{AB01918B-B663-4449-BAA3-04E293229795}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
